--- a/excel_routes/route_AJF_CCE_threats.xlsx
+++ b/excel_routes/route_AJF_CCE_threats.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -523,7 +523,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>09-APR-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -537,22 +537,22 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>950</v>
+        <v>1101</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>958</v>
+        <v>1293</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-8</v>
+        <v>-192</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -568,7 +568,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>09-APR-26</t>
+          <t>23-MAY-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -585,19 +585,19 @@
         <v>950</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>958</v>
+        <v>1098</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-8</v>
+        <v>-148</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -613,7 +613,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>16-APR-26</t>
+          <t>24-JUN-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -623,26 +623,26 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-110</t>
+          <t>Nile Air NP-120</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
         <v>1101</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1128</v>
+        <v>1150</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-27</v>
+        <v>-49</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -658,7 +658,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>16-APR-26</t>
+          <t>01-JUL-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -668,26 +668,26 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-110</t>
+          <t>Nile Air NP-120</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1101</v>
+        <v>950</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1128</v>
+        <v>980</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-27</v>
+        <v>-30</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -703,7 +703,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>23-APR-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -717,19 +717,19 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>550</v>
+        <v>950</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>578</v>
+        <v>1060</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-28</v>
+        <v>-110</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
         <v>0</v>
@@ -748,7 +748,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>23-APR-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -758,23 +758,23 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-110</t>
+          <t>Nile Air NP-120</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>550</v>
+        <v>745</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>578</v>
+        <v>790</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-28</v>
+        <v>-45</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
         <v>0</v>
@@ -793,7 +793,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>29-APR-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -803,23 +803,23 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-120</t>
+          <t>Nile Air NP-110</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>550</v>
+        <v>745</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>578</v>
+        <v>790</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-28</v>
+        <v>-45</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
         <v>0</v>
@@ -838,7 +838,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>29-APR-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -852,19 +852,19 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>550</v>
+        <v>745</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>578</v>
+        <v>790</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-28</v>
+        <v>-45</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
         <v>0</v>
@@ -883,7 +883,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>30-APR-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -897,19 +897,19 @@
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>550</v>
+        <v>745</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>578</v>
+        <v>790</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-28</v>
+        <v>-45</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
         <v>0</v>
@@ -928,7 +928,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>30-APR-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -938,23 +938,23 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-110</t>
+          <t>Nile Air NP-120</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>550</v>
+        <v>745</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>578</v>
+        <v>790</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-28</v>
+        <v>-45</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
         <v>0</v>
@@ -973,7 +973,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>06-MAY-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -983,23 +983,23 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-120</t>
+          <t>Nile Air NP-110</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>550</v>
+        <v>745</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>578</v>
+        <v>790</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-28</v>
+        <v>-45</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
         <v>0</v>
@@ -1018,7 +1018,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>06-MAY-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1032,19 +1032,19 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>550</v>
+        <v>745</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>578</v>
+        <v>790</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-28</v>
+        <v>-45</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
         <v>0</v>
@@ -1063,7 +1063,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>07-MAY-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1077,19 +1077,19 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>550</v>
+        <v>745</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>578</v>
+        <v>790</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-28</v>
+        <v>-45</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
         <v>0</v>
@@ -1108,7 +1108,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>07-MAY-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1118,23 +1118,23 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-110</t>
+          <t>Nile Air NP-120</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>550</v>
+        <v>421</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>578</v>
+        <v>482</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-28</v>
+        <v>-61</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
         <v>0</v>
@@ -1153,7 +1153,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>13-MAY-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1163,23 +1163,23 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-120</t>
+          <t>Nile Air NP-110</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>550</v>
+        <v>421</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>578</v>
+        <v>482</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-28</v>
+        <v>-61</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
         <v>0</v>
@@ -1198,7 +1198,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>13-MAY-26</t>
+          <t>30-SEP-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1212,19 +1212,19 @@
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>550</v>
+        <v>421</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>578</v>
+        <v>482</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-28</v>
+        <v>-61</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
         <v>0</v>
@@ -1235,186 +1235,6 @@
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>14-MAY-26</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>SM-322</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-110</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>550</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>578</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>-28</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>14-MAY-26</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>SM-322</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-110</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>550</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>578</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>-28</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="I19" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>28-MAY-26</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>SM-322</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-110</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>550</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>578</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>-28</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>28-MAY-26</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>SM-322</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-110</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>550</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>578</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>-28</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_AJF_CCE_threats.xlsx
+++ b/excel_routes/route_AJF_CCE_threats.xlsx
@@ -537,13 +537,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1101</v>
+        <v>950</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>1293</v>
+        <v>1020</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-192</v>
+        <v>-70</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -568,7 +568,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>23-MAY-26</t>
+          <t>28-MAY-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -582,13 +582,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>950</v>
+        <v>845</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1098</v>
+        <v>850</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-148</v>
+        <v>-5</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -613,7 +613,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>24-JUN-26</t>
+          <t>17-JUN-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -627,13 +627,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1101</v>
+        <v>845</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1150</v>
+        <v>850</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-49</v>
+        <v>-5</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -658,7 +658,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>01-JUL-26</t>
+          <t>24-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -672,13 +672,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>950</v>
+        <v>1101</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>980</v>
+        <v>1150</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-30</v>
+        <v>-49</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -703,7 +703,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>01-JUL-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-110</t>
+          <t>Nile Air NP-120</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
         <v>950</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1060</v>
+        <v>980</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-110</v>
+        <v>-30</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
